--- a/USJ/USJ_import_stock_receive_20260728_final4.xlsx
+++ b/USJ/USJ_import_stock_receive_20260728_final4.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Review_Flags" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Resolved" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="to_be_resolved" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Flagged_New_Items" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$Z$402</definedName>
@@ -21,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -105,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -118,6 +121,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z402"/>
+  <dimension ref="A1:Z506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -866,7 +871,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -926,7 +931,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1156,7 +1161,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>LMN-ERKA-USA-0001</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1806,7 +1811,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1901,7 +1906,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2442,7 +2447,7 @@
       </c>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="R32" s="5" t="inlineStr">
         <is>
@@ -2516,7 +2521,7 @@
       </c>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2868,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>231</v>
+        <v>311</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2920,7 +2925,7 @@
       </c>
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3432,7 +3437,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3853,7 +3858,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -4268,7 +4273,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -4433,7 +4438,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -4757,7 +4762,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -5688,7 +5693,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -5817,7 +5822,7 @@
       </c>
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
@@ -5943,7 +5948,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -5988,7 +5993,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
       </c>
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
@@ -6259,7 +6264,7 @@
       </c>
       <c r="P99" s="2" t="n"/>
       <c r="Q99" s="2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
@@ -6526,7 +6531,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -6856,7 +6861,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="R110" t="inlineStr">
         <is>
@@ -6911,7 +6916,7 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="R111" t="inlineStr">
         <is>
@@ -7074,7 +7079,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="R114" t="inlineStr">
         <is>
@@ -7129,7 +7134,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>
@@ -7267,7 +7272,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="R117" t="inlineStr">
         <is>
@@ -7463,7 +7468,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="R121" t="inlineStr">
         <is>
@@ -7713,7 +7718,7 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
@@ -7748,7 +7753,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
@@ -7888,7 +7893,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
@@ -8162,7 +8167,7 @@
       </c>
       <c r="P135" s="2" t="n"/>
       <c r="Q135" s="2" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
@@ -8457,7 +8462,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
@@ -8497,7 +8502,7 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
@@ -8566,7 +8571,7 @@
       </c>
       <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="n">
-        <v>154</v>
+        <v>275</v>
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
@@ -8855,7 +8860,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R147" t="inlineStr">
         <is>
@@ -8920,7 +8925,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
@@ -9317,7 +9322,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>56</v>
+        <v>224</v>
       </c>
       <c r="R155" t="inlineStr">
         <is>
@@ -9352,7 +9357,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>56</v>
+        <v>224</v>
       </c>
       <c r="R156" t="inlineStr">
         <is>
@@ -9693,7 +9698,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="R161" t="inlineStr">
         <is>
@@ -9738,7 +9743,7 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
@@ -9783,7 +9788,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
@@ -9828,7 +9833,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="R164" t="inlineStr">
         <is>
@@ -9902,7 +9907,7 @@
       </c>
       <c r="P165" s="2" t="n"/>
       <c r="Q165" s="2" t="n">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="R165" s="2" t="inlineStr">
         <is>
@@ -10017,7 +10022,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="R167" t="inlineStr">
         <is>
@@ -10117,7 +10122,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="R169" t="inlineStr">
         <is>
@@ -10402,7 +10407,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="R174" t="inlineStr">
         <is>
@@ -10497,7 +10502,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="R176" t="inlineStr">
         <is>
@@ -10607,7 +10612,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="R178" t="inlineStr">
         <is>
@@ -10776,7 +10781,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="R181" t="inlineStr">
         <is>
@@ -11056,7 +11061,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="R187" t="inlineStr">
         <is>
@@ -11106,7 +11111,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>112</v>
+        <v>1106</v>
       </c>
       <c r="R188" t="inlineStr">
         <is>
@@ -11156,7 +11161,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="R189" t="inlineStr">
         <is>
@@ -11201,7 +11206,7 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="R190" t="inlineStr">
         <is>
@@ -11366,7 +11371,7 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="R193" t="inlineStr">
         <is>
@@ -11471,7 +11476,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="R195" t="inlineStr">
         <is>
@@ -11516,7 +11521,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="R196" t="inlineStr">
         <is>
@@ -11576,7 +11581,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>25</v>
+        <v>294</v>
       </c>
       <c r="R197" t="inlineStr">
         <is>
@@ -11681,7 +11686,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="R199" t="inlineStr">
         <is>
@@ -11836,7 +11841,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -11886,7 +11891,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="R203" t="inlineStr">
         <is>
@@ -12148,7 +12153,7 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="R207" t="inlineStr">
         <is>
@@ -12212,7 +12217,7 @@
       </c>
       <c r="P208" s="2" t="n"/>
       <c r="Q208" s="2" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="R208" s="2" t="inlineStr">
         <is>
@@ -12332,7 +12337,7 @@
       </c>
       <c r="P210" s="2" t="n"/>
       <c r="Q210" s="2" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="R210" s="2" t="inlineStr">
         <is>
@@ -12700,7 +12705,7 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="R217" t="inlineStr">
         <is>
@@ -13065,7 +13070,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R225" t="inlineStr">
         <is>
@@ -13468,7 +13473,7 @@
       </c>
       <c r="P231" s="2" t="n"/>
       <c r="Q231" s="2" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
@@ -13603,7 +13608,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="R233" t="inlineStr">
         <is>
@@ -13763,7 +13768,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="R237" t="inlineStr">
         <is>
@@ -13823,7 +13828,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R238" t="inlineStr">
         <is>
@@ -14091,7 +14096,7 @@
       </c>
       <c r="P242" s="2" t="n"/>
       <c r="Q242" s="2" t="n">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="R242" s="2" t="inlineStr">
         <is>
@@ -14160,7 +14165,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="R243" t="inlineStr">
         <is>
@@ -14280,7 +14285,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="R245" t="inlineStr">
         <is>
@@ -14590,7 +14595,7 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="R251" t="inlineStr">
         <is>
@@ -14710,7 +14715,7 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R253" t="inlineStr">
         <is>
@@ -14770,7 +14775,7 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -14815,7 +14820,7 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -14970,7 +14975,7 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="R258" t="inlineStr">
         <is>
@@ -15175,7 +15180,7 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>805</v>
+        <v>535</v>
       </c>
       <c r="R262" t="inlineStr">
         <is>
@@ -15289,7 +15294,7 @@
       </c>
       <c r="P264" s="2" t="n"/>
       <c r="Q264" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R264" s="2" t="inlineStr">
         <is>
@@ -15367,7 +15372,7 @@
       </c>
       <c r="P265" s="2" t="n"/>
       <c r="Q265" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R265" s="2" t="inlineStr">
         <is>
@@ -15656,7 +15661,7 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="R270" t="inlineStr">
         <is>
@@ -15776,7 +15781,7 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="R272" t="inlineStr">
         <is>
@@ -15846,7 +15851,7 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R274" t="inlineStr">
         <is>
@@ -15970,7 +15975,7 @@
       </c>
       <c r="P276" s="2" t="n"/>
       <c r="Q276" s="2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="R276" s="2" t="inlineStr">
         <is>
@@ -16039,7 +16044,7 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R277" t="inlineStr">
         <is>
@@ -16108,7 +16113,7 @@
       </c>
       <c r="P278" s="2" t="n"/>
       <c r="Q278" s="2" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="R278" s="2" t="inlineStr">
         <is>
@@ -16374,7 +16379,7 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="R283" t="inlineStr">
         <is>
@@ -16409,7 +16414,7 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="R284" t="inlineStr">
         <is>
@@ -16464,7 +16469,7 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="R285" t="inlineStr">
         <is>
@@ -16524,7 +16529,7 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>16</v>
+        <v>224</v>
       </c>
       <c r="R286" t="inlineStr">
         <is>
@@ -16574,7 +16579,7 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R287" t="inlineStr">
         <is>
@@ -16684,7 +16689,7 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="R289" t="inlineStr">
         <is>
@@ -16744,7 +16749,7 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -16848,7 +16853,7 @@
       </c>
       <c r="P292" s="2" t="n"/>
       <c r="Q292" s="2" t="n">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="R292" s="2" t="inlineStr">
         <is>
@@ -16906,7 +16911,7 @@
       </c>
       <c r="P293" s="2" t="n"/>
       <c r="Q293" s="2" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="R293" s="2" t="inlineStr">
         <is>
@@ -16967,7 +16972,7 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="R294" t="inlineStr">
         <is>
@@ -17111,7 +17116,7 @@
       </c>
       <c r="P297" s="5" t="n"/>
       <c r="Q297" s="5" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="R297" s="5" t="inlineStr">
         <is>
@@ -17180,7 +17185,7 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="R298" t="inlineStr">
         <is>
@@ -17239,7 +17244,7 @@
       </c>
       <c r="P299" s="2" t="n"/>
       <c r="Q299" s="2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R299" s="2" t="inlineStr">
         <is>
@@ -17301,7 +17306,7 @@
       </c>
       <c r="P300" s="2" t="n"/>
       <c r="Q300" s="2" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="R300" s="2" t="inlineStr">
         <is>
@@ -17421,7 +17426,7 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="R302" t="inlineStr">
         <is>
@@ -17871,7 +17876,7 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R311" t="inlineStr">
         <is>
@@ -17996,7 +18001,7 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="R313" t="inlineStr">
         <is>
@@ -18061,7 +18066,7 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="R314" t="inlineStr">
         <is>
@@ -18121,7 +18126,7 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="R315" t="inlineStr">
         <is>
@@ -18409,7 +18414,7 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R320" t="inlineStr">
         <is>
@@ -18469,7 +18474,7 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R321" t="inlineStr">
         <is>
@@ -18529,7 +18534,7 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R322" t="inlineStr">
         <is>
@@ -18589,7 +18594,7 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="R323" t="inlineStr">
         <is>
@@ -18629,7 +18634,7 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="R324" t="inlineStr">
         <is>
@@ -18789,7 +18794,7 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="R327" t="inlineStr">
         <is>
@@ -18884,7 +18889,7 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="R329" t="inlineStr">
         <is>
@@ -18934,7 +18939,7 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>806</v>
+        <v>483</v>
       </c>
       <c r="R330" t="inlineStr">
         <is>
@@ -18977,7 +18982,7 @@
       <c r="K331" s="2" t="n"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>GRP-BLK-EGY-0001</t>
+          <t>GRP-BLKSDLS-EGY-0002</t>
         </is>
       </c>
       <c r="M331" s="2" t="inlineStr">
@@ -18993,7 +18998,7 @@
       </c>
       <c r="P331" s="2" t="n"/>
       <c r="Q331" s="2" t="n">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
@@ -19062,7 +19067,7 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="R332" t="inlineStr">
         <is>
@@ -19117,7 +19122,7 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R333" t="inlineStr">
         <is>
@@ -19207,7 +19212,7 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="R335" t="inlineStr">
         <is>
@@ -19272,7 +19277,7 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>480</v>
+        <v>434</v>
       </c>
       <c r="R336" t="inlineStr">
         <is>
@@ -19332,7 +19337,7 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="R337" t="inlineStr">
         <is>
@@ -19387,7 +19392,7 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="R338" t="inlineStr">
         <is>
@@ -19447,7 +19452,7 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>145</v>
+        <v>439</v>
       </c>
       <c r="R339" t="inlineStr">
         <is>
@@ -19492,7 +19497,7 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="R340" t="inlineStr">
         <is>
@@ -19537,7 +19542,7 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>155</v>
+        <v>479</v>
       </c>
       <c r="R341" t="inlineStr">
         <is>
@@ -19770,7 +19775,7 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="R345" t="inlineStr">
         <is>
@@ -19825,7 +19830,7 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>65</v>
+        <v>440</v>
       </c>
       <c r="R346" t="inlineStr">
         <is>
@@ -20264,7 +20269,7 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>345</v>
+        <v>250</v>
       </c>
       <c r="R353" t="inlineStr">
         <is>
@@ -20319,7 +20324,7 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R354" t="inlineStr">
         <is>
@@ -20444,7 +20449,7 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="R356" t="inlineStr">
         <is>
@@ -20504,7 +20509,7 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="R357" t="inlineStr">
         <is>
@@ -20564,7 +20569,7 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="R358" t="inlineStr">
         <is>
@@ -20621,7 +20626,7 @@
       </c>
       <c r="P359" s="5" t="n"/>
       <c r="Q359" s="5" t="n">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="R359" s="5" t="inlineStr">
         <is>
@@ -20675,7 +20680,7 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R360" t="inlineStr">
         <is>
@@ -20744,7 +20749,7 @@
       </c>
       <c r="P361" s="2" t="n"/>
       <c r="Q361" s="2" t="n">
-        <v>720</v>
+        <v>220</v>
       </c>
       <c r="R361" s="2" t="inlineStr">
         <is>
@@ -20864,7 +20869,7 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R363" t="inlineStr">
         <is>
@@ -20926,7 +20931,7 @@
       </c>
       <c r="P364" s="2" t="n"/>
       <c r="Q364" s="2" t="n">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="R364" s="2" t="inlineStr">
         <is>
@@ -20984,7 +20989,7 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="R365" t="inlineStr">
         <is>
@@ -21046,7 +21051,7 @@
       </c>
       <c r="P366" s="2" t="n"/>
       <c r="Q366" s="2" t="n">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="R366" s="2" t="inlineStr">
         <is>
@@ -21174,7 +21179,7 @@
       </c>
       <c r="P368" s="5" t="n"/>
       <c r="Q368" s="5" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="R368" s="5" t="inlineStr">
         <is>
@@ -21235,7 +21240,7 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="R369" t="inlineStr">
         <is>
@@ -21280,7 +21285,7 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="R370" t="inlineStr">
         <is>
@@ -21394,7 +21399,7 @@
       </c>
       <c r="P372" s="2" t="n"/>
       <c r="Q372" s="2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="R372" s="2" t="inlineStr">
         <is>
@@ -21463,7 +21468,7 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="R373" t="inlineStr">
         <is>
@@ -21592,7 +21597,7 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="R375" t="inlineStr">
         <is>
@@ -21656,7 +21661,7 @@
       </c>
       <c r="P376" s="5" t="n"/>
       <c r="Q376" s="5" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="R376" s="5" t="inlineStr">
         <is>
@@ -21714,7 +21719,7 @@
       </c>
       <c r="P377" s="5" t="n"/>
       <c r="Q377" s="5" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="R377" s="5" t="inlineStr">
         <is>
@@ -21845,7 +21850,7 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="R379" t="inlineStr">
         <is>
@@ -21890,7 +21895,7 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>320</v>
+        <v>64</v>
       </c>
       <c r="R380" t="inlineStr">
         <is>
@@ -21959,7 +21964,7 @@
       </c>
       <c r="P381" s="2" t="n"/>
       <c r="Q381" s="2" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="R381" s="2" t="inlineStr">
         <is>
@@ -22075,7 +22080,7 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>430</v>
+        <v>162</v>
       </c>
       <c r="R383" t="inlineStr">
         <is>
@@ -22205,7 +22210,7 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="R386" t="inlineStr">
         <is>
@@ -22334,7 +22339,7 @@
       </c>
       <c r="P388" s="2" t="n"/>
       <c r="Q388" s="2" t="n">
-        <v>600</v>
+        <v>261</v>
       </c>
       <c r="R388" s="2" t="inlineStr">
         <is>
@@ -22834,7 +22839,7 @@
       </c>
       <c r="P399" s="2" t="n"/>
       <c r="Q399" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R399" s="2" t="inlineStr">
         <is>
@@ -22961,9 +22966,3961 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="R402" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Doc245</t>
+        </is>
+      </c>
+      <c r="B403" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>APL-RYLBTY-SA-0005</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>SA ROYAL BEAUTY APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>USJ-PPO-0289</t>
+        </is>
+      </c>
+      <c r="Q403" t="n">
+        <v>56</v>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Doc246</t>
+        </is>
+      </c>
+      <c r="B404" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>APL-RDFJI-SA-0094</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>SA KANGB RED FUJI APPLE 18KG 150</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>USJ-B-KEE-3527</t>
+        </is>
+      </c>
+      <c r="Q404" t="n">
+        <v>38</v>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Doc246</t>
+        </is>
+      </c>
+      <c r="B405" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>APL-RDFJI-SA-0095</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>SA KANGB RED FUJI APPLE 18KG 180</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>USJ-B-KEE-3527</t>
+        </is>
+      </c>
+      <c r="Q405" t="n">
+        <v>52</v>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Doc247</t>
+        </is>
+      </c>
+      <c r="B406" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>APL-RDFJI-SA-0066</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>SA NVF RED FUJI APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>USJ-GL-7044</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>56</v>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Doc248</t>
+        </is>
+      </c>
+      <c r="B407" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0001</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>USJ-GL-9511</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>28</v>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Doc249</t>
+        </is>
+      </c>
+      <c r="B408" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0002</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>USJ-GL-9803</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>84</v>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Doc249</t>
+        </is>
+      </c>
+      <c r="B409" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0003</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 150</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>USJ-GL-9803</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>56</v>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Doc249</t>
+        </is>
+      </c>
+      <c r="B410" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0018</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>USJ-GL-9803</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>31</v>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Doc249</t>
+        </is>
+      </c>
+      <c r="B411" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0001</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>USJ-GL-9803</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>25</v>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Doc249</t>
+        </is>
+      </c>
+      <c r="B412" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0001</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>USJ-GL-9803</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>56</v>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Doc250</t>
+        </is>
+      </c>
+      <c r="B413" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>APL-PRMRSTR-NZ-0003</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>NZ PREMIER START PG APPLE 17.5KG 150</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>USJ-GL-6647</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>51</v>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Doc251</t>
+        </is>
+      </c>
+      <c r="B414" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>APL-PRMRSTR-NZ-0001</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>NZ PREMIER STAR PG APPLE 17.5KG</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>USJ-GL-3729</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>120</v>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Doc252</t>
+        </is>
+      </c>
+      <c r="B415" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0035</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG 18KG 135</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>USJ-GL-7754</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>56</v>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Doc253</t>
+        </is>
+      </c>
+      <c r="B416" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0035</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>USJ-GL-8660</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>42</v>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Doc254</t>
+        </is>
+      </c>
+      <c r="B417" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0038</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG 90</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>USJ-GL-4696</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>91</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Doc254</t>
+        </is>
+      </c>
+      <c r="B418" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0038</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>USJ-GL-4696</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>56</v>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Doc254</t>
+        </is>
+      </c>
+      <c r="B419" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0038</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG 120</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>USJ-GL-4696</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>56</v>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Doc255</t>
+        </is>
+      </c>
+      <c r="B420" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>APL-ENVY-NZ-0035</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>USJ-GL-2974</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>112</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Doc256</t>
+        </is>
+      </c>
+      <c r="B421" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>APL-LUMI-NZ-0003</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE (2 LAYER) 8.5KG 70</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>USJ-GL-0367</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>39</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Doc256</t>
+        </is>
+      </c>
+      <c r="B422" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>APL-LUMI-NZ-0003</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>USJ-GL-0367</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>5</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Doc256</t>
+        </is>
+      </c>
+      <c r="B423" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>APL-LUMI-NZ-0001</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG 110</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>USJ-GL-0367</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>8</v>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Doc256</t>
+        </is>
+      </c>
+      <c r="B424" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>APL-LUMI-NZ-0002</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG 120</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>USJ-GL-0367</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>4</v>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Doc257</t>
+        </is>
+      </c>
+      <c r="B425" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0011</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>SA GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>USJ-GL-7128</t>
+        </is>
+      </c>
+      <c r="Q425" t="n">
+        <v>22</v>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Doc258</t>
+        </is>
+      </c>
+      <c r="B426" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0009</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>SA INSEA GRANNY SMITH APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>USJ-GL-6628</t>
+        </is>
+      </c>
+      <c r="Q426" t="n">
+        <v>11</v>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Doc259</t>
+        </is>
+      </c>
+      <c r="B427" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0009</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>SA KANGB GRANNY SMITH APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>USJ-GL-6049</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>128</v>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Doc259</t>
+        </is>
+      </c>
+      <c r="B428" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0033</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>SA C5 GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>USJ-GL-6049</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>26</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Doc260</t>
+        </is>
+      </c>
+      <c r="B429" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0006</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH 18KG 120</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>USJ-UPT9630</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>47</v>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Doc261</t>
+        </is>
+      </c>
+      <c r="B430" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0008</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH 18KG 150</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>USJ-UPT5788</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>15</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Doc262</t>
+        </is>
+      </c>
+      <c r="B431" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0011</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>USJ-B-KEE-3946</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>30</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Doc263</t>
+        </is>
+      </c>
+      <c r="B432" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0007</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 135</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>USJ-GL-1143</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>56</v>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Doc264</t>
+        </is>
+      </c>
+      <c r="B433" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0007</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 135</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>USJ-GL-3522</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>26</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Doc265</t>
+        </is>
+      </c>
+      <c r="B434" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0003</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>SA KROMCO GRANNY SMITH 18KG 90</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>USJ-MK26071062</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>86</v>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Doc265</t>
+        </is>
+      </c>
+      <c r="B435" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>APL-GS-SA-0005</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>SA KROMCO GRANNY SMITH 18KG 110</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>USJ-MK26071062</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>56</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Doc266</t>
+        </is>
+      </c>
+      <c r="B436" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>LMN-ERKA-SA-0017</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>SA SY LEMON 15KG 113</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>USJ-GL-7270</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>160</v>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Doc267</t>
+        </is>
+      </c>
+      <c r="B437" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>LMN-ERKA-SA-0016</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>SA SY LEMON 15KG 100</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>USJ-GL-7952</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>160</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Doc268</t>
+        </is>
+      </c>
+      <c r="B438" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>MDRN-NOVA-SA-0001</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>SA NATBL NOVA MANDARIN 10KG 3</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>USJ-GL-8306</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>33</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Doc269</t>
+        </is>
+      </c>
+      <c r="B439" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>MDRN-NDRCOT-SA-0011</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG 2</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>USJ-GL-5257</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>104</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Doc269</t>
+        </is>
+      </c>
+      <c r="B440" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>MDRN-NDRCOT-SA-0011</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>USJ-GL-5257</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>254</v>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Doc269</t>
+        </is>
+      </c>
+      <c r="B441" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>MDRN-NDRCOT-SA-0011</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG 3</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>USJ-GL-5257</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>104</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Doc270</t>
+        </is>
+      </c>
+      <c r="B442" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>OR-VAL-SA-0002</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>SA VALENCIA 15KG 72</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>USJ-FF0840</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>40</v>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Doc271</t>
+        </is>
+      </c>
+      <c r="B443" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>OR-VAL-SA-0002</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 72</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>USJ-GL-4717</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>20</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Doc271</t>
+        </is>
+      </c>
+      <c r="B444" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>OR-VAL-SA-0015</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 88</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>USJ-GL-4717</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>75</v>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Doc271</t>
+        </is>
+      </c>
+      <c r="B445" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>OR-VAL-SA-0015</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 88</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>USJ-GL-4717</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>144</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Doc271</t>
+        </is>
+      </c>
+      <c r="B446" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>OR-VAL-SA-0048</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 105</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>USJ-GL-4717</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>80</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Doc272</t>
+        </is>
+      </c>
+      <c r="B447" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>OR-NAV-CN-0004</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>CHINA NAVEL 14KG 64</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>USJ-PPO-8849</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>4</v>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Doc273</t>
+        </is>
+      </c>
+      <c r="B448" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>OR-NAV-SA-0086</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>SA SY NAVEL ORANGE 15KG 56</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>USJ-GL-6780</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>107</v>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Doc274</t>
+        </is>
+      </c>
+      <c r="B449" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>OR-NAV-SA-0029</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 60</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>USJ-GL-4070</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>62</v>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Doc274</t>
+        </is>
+      </c>
+      <c r="B450" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>OR-NAV-SA-0029</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 60</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>USJ-GL-4070</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>30</v>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Doc274</t>
+        </is>
+      </c>
+      <c r="B451" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>OR-NAV-SA-0030</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 65</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>USJ-GL-4070</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>2</v>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Doc275</t>
+        </is>
+      </c>
+      <c r="B452" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>OR-CARA-SA-0064</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>SA CARA CARA ORANGES 15KG 55</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>USJ-GL-3877</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>45</v>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Doc276</t>
+        </is>
+      </c>
+      <c r="B453" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>OR-CARA-SA-0029</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 60</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>USJ-1130</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>27</v>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Doc276</t>
+        </is>
+      </c>
+      <c r="B454" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>OR-CARA-SA-0030</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 65</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>USJ-1130</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>26</v>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Doc276</t>
+        </is>
+      </c>
+      <c r="B455" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>OR-CARA-SA-0033</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 88</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>USJ-1130</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>175</v>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Doc276</t>
+        </is>
+      </c>
+      <c r="B456" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>OR-CARA-SA-0065</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 105</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>USJ-1130</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>219</v>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Doc277</t>
+        </is>
+      </c>
+      <c r="B457" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>POM-NA-IND-0003</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>INDIA POMEGRANATES 3KG 10</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>USJ-GL-6990</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>109</v>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Doc277</t>
+        </is>
+      </c>
+      <c r="B458" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>POM-NA-IND-0004</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>INDIA POMEGRANATES 3KG 12</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>USJ-GL-6990</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>360</v>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Doc278</t>
+        </is>
+      </c>
+      <c r="B459" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>PR-HUNGGN-CN-0006</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>CHINA HUANG GUAN 13KG 48</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>USJ-FF-1378</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>56</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Doc279</t>
+        </is>
+      </c>
+      <c r="B460" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>PR-FRGNT-CN-0008</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 170GM</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>USJ-PPO-0599</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>42</v>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Doc279</t>
+        </is>
+      </c>
+      <c r="B461" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>PR-FRGNT-CN-0008</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 170GM</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>USJ-PPO-0599</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>90</v>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Doc279</t>
+        </is>
+      </c>
+      <c r="B462" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>PR-FRGNT-CN-0008</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 180GM</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>USJ-PPO-0599</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>72</v>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Doc280</t>
+        </is>
+      </c>
+      <c r="B463" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>PR-PCKHM-SA-0020</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>SA DUTOIT PACKHAMS TRIUMPH PEAR 12KG 60</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>USJ-GL-4758</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>28</v>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Doc281</t>
+        </is>
+      </c>
+      <c r="B464" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>PR-PCKHM-SA-0007</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>SA C5 PACKHAM PEAR 12KG 60</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>USJ-GL-7350</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>240</v>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Doc282</t>
+        </is>
+      </c>
+      <c r="B465" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>GRP-RDGLB-CN-0005</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>CHINA RED GLOBE 6.5KG 11 X 800GM</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>USJ-FF-1320</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>35</v>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Doc283</t>
+        </is>
+      </c>
+      <c r="B466" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>GRP-IVORY-USA-0001</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>USA SUPERSWEET IVORY GRAPE 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>USJ-AIR-2912</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>1</v>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Doc284</t>
+        </is>
+      </c>
+      <c r="B467" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>GRP-SGRCRCH-USA-0001</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>USA BLUE STONE SUGAR CRUNCH GRAPES 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>USJ-AIR-4752</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>100</v>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Doc284</t>
+        </is>
+      </c>
+      <c r="B468" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>GRP-MDNGTBTY-USA-0002</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>USA AIR CHIEF MIDNIGHT BEAUTY GRAPES 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>USJ-AIR-4752</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>25</v>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Doc284</t>
+        </is>
+      </c>
+      <c r="B469" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>GRP-ADRA-USA-0001</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>USA KRISSY 8.6KG / BEBOP 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>USJ-AIR-4752</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>45</v>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Doc285</t>
+        </is>
+      </c>
+      <c r="B470" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>CHINA SHINE MUSCAT 8X500</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>USJ-PPO-3906</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>7</v>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Doc286</t>
+        </is>
+      </c>
+      <c r="B471" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>CHINA GB SHINE MUSCAT 10X500G 22MM</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>USJ-GL-5160</t>
+        </is>
+      </c>
+      <c r="Q471" t="n">
+        <v>230</v>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Doc287</t>
+        </is>
+      </c>
+      <c r="B472" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G 22MM</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>USJ-GL-8283</t>
+        </is>
+      </c>
+      <c r="Q472" t="n">
+        <v>215</v>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Doc287</t>
+        </is>
+      </c>
+      <c r="B473" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>USJ-GL-8283</t>
+        </is>
+      </c>
+      <c r="Q473" t="n">
+        <v>115</v>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Doc287</t>
+        </is>
+      </c>
+      <c r="B474" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>USJ-GL-8283</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>230</v>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Doc287</t>
+        </is>
+      </c>
+      <c r="B475" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>USJ-GL-8283</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>110</v>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Doc288</t>
+        </is>
+      </c>
+      <c r="B476" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>CHINA GENERIC SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>USJ-GL-9804</t>
+        </is>
+      </c>
+      <c r="Q476" t="n">
+        <v>920</v>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Doc289</t>
+        </is>
+      </c>
+      <c r="B477" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>GRP-ATMRYL-CN-0001</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>CHINA GB AUTUMN ROYAL GRAPE (BLACK SEED) 10X500GM 20-28MM</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>USJ-GL-0443</t>
+        </is>
+      </c>
+      <c r="Q477" t="n">
+        <v>115</v>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Doc290</t>
+        </is>
+      </c>
+      <c r="B478" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>GRP-BLK-EGY-0001</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>USJ-GL-2552</t>
+        </is>
+      </c>
+      <c r="Q478" t="n">
+        <v>125</v>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Doc290</t>
+        </is>
+      </c>
+      <c r="B479" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>GRP-BLK-EGY-0001</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>USJ-GL-2552</t>
+        </is>
+      </c>
+      <c r="Q479" t="n">
+        <v>75</v>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Doc290</t>
+        </is>
+      </c>
+      <c r="B480" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>GRP-BLK-EGY-0001</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>USJ-GL-2552</t>
+        </is>
+      </c>
+      <c r="Q480" t="n">
+        <v>125</v>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Doc291</t>
+        </is>
+      </c>
+      <c r="B481" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>GRP-BLKSDLS-EGY-0002</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>EGYPT AGRO VALLEY GRAPE 10X500GM</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>USJ-GL-5426</t>
+        </is>
+      </c>
+      <c r="Q481" t="n">
+        <v>404</v>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Doc292</t>
+        </is>
+      </c>
+      <c r="B482" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>GRP-CRMSN-CN-0001</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>CHINA CRIMSON GRAPE 10X500G</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>USJ-GL-1394</t>
+        </is>
+      </c>
+      <c r="Q482" t="n">
+        <v>6</v>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Doc293</t>
+        </is>
+      </c>
+      <c r="B483" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>DRGNFRT-WTE-VIE-0001</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 18</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>USJ-FF-1378</t>
+        </is>
+      </c>
+      <c r="Q483" t="n">
+        <v>143</v>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Doc294</t>
+        </is>
+      </c>
+      <c r="B484" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>DRGNFRT-WTE-VIE-0001</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 18</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>USJ-4657</t>
+        </is>
+      </c>
+      <c r="Q484" t="n">
+        <v>1306</v>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Doc294</t>
+        </is>
+      </c>
+      <c r="B485" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>DRGNFRT-WTE-VIE-0001</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>USJ-4657</t>
+        </is>
+      </c>
+      <c r="Q485" t="n">
+        <v>280</v>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Doc294</t>
+        </is>
+      </c>
+      <c r="B486" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>DRGNFRT-WTE-VIE-0002</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 24</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>USJ-4657</t>
+        </is>
+      </c>
+      <c r="Q486" t="n">
+        <v>384</v>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Doc294</t>
+        </is>
+      </c>
+      <c r="B487" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>DRGNFRT-WTE-VIE-0001</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>USJ-4657</t>
+        </is>
+      </c>
+      <c r="Q487" t="n">
+        <v>280</v>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Doc295</t>
+        </is>
+      </c>
+      <c r="B488" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>BLUBRY-ATLSBLU-ZWE-0001</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>ZIMBABWE BLUEBERRY (JUMBO TUBE) 10X200G 18MM</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>USJ-FF26071376</t>
+        </is>
+      </c>
+      <c r="Q488" t="n">
+        <v>38</v>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Doc296</t>
+        </is>
+      </c>
+      <c r="B489" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>STBRY-SWTDLNG-USA-0001</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>USA STRAWBERRIES - SWEET DARLING 12X125GM 13 X 250G</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>USJ-AIR-5352</t>
+        </is>
+      </c>
+      <c r="Q489" t="n">
+        <v>240</v>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Doc297</t>
+        </is>
+      </c>
+      <c r="B490" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>CHRY-DRKSWT-USA-0001</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>USA BORTON FRUIT SWEET CHERRY 9KG 9.5ROW</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>USJ-AIR-2360</t>
+        </is>
+      </c>
+      <c r="Q490" t="n">
+        <v>1</v>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Doc298</t>
+        </is>
+      </c>
+      <c r="B491" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>CHRY-LPN-USA-0014</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>USA GOLD PRIZE SWEET CHERRY 5KG</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>USJ-AIR-2962</t>
+        </is>
+      </c>
+      <c r="Q491" t="n">
+        <v>195</v>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Doc299</t>
+        </is>
+      </c>
+      <c r="B492" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>PCH-WTE-KOR-0001</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>KOREA WHITE PEACHES 2PCS 2S 2PCS X 6PKT</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>USJ-AIR-1944</t>
+        </is>
+      </c>
+      <c r="Q492" t="n">
+        <v>96</v>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Doc300</t>
+        </is>
+      </c>
+      <c r="B493" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>PLM-BLK-USA-0001</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>USA MOUNTAIN VIEW EMERALD BEAUTY PLUMS 11.3KG 16X1LB</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>USJ-AIR-1863</t>
+        </is>
+      </c>
+      <c r="Q493" t="n">
+        <v>51</v>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B494" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>MNGO-YLW-CN-0001</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 14</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q494" t="n">
+        <v>154</v>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B495" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>MNGO-YLW-CN-0001</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 16</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q495" t="n">
+        <v>221</v>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B496" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>MNGO-YLW-CN-0002</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 18</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q496" t="n">
+        <v>150</v>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B497" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>MNGO-YLW-CN-0003</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 20</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>137</v>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B498" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>MNGO-GRN-CN-0001</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 16</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q498" t="n">
+        <v>36</v>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B499" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>MNGO-GRN-CN-0001</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 18</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q499" t="n">
+        <v>85</v>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B500" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>MNGO-GRN-CN-0002</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 20</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q500" t="n">
+        <v>106</v>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B501" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>MNGO-GRN-CN-0003</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 24</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q501" t="n">
+        <v>478</v>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Doc301</t>
+        </is>
+      </c>
+      <c r="B502" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>MNGO-GRN-CN-0001</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 28</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>USJ-9949</t>
+        </is>
+      </c>
+      <c r="Q502" t="n">
+        <v>20</v>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Doc302</t>
+        </is>
+      </c>
+      <c r="B503" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>KWI-SUNGLD-NZ-0009</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>USJ-PPO-3748</t>
+        </is>
+      </c>
+      <c r="Q503" t="n">
+        <v>150</v>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Doc302</t>
+        </is>
+      </c>
+      <c r="B504" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>KWI-SUNGLD-NZ-0009</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>USJ-PPO-3748</t>
+        </is>
+      </c>
+      <c r="Q504" t="n">
+        <v>110</v>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Doc303</t>
+        </is>
+      </c>
+      <c r="B505" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>KWI-SUNGLD-NZ-0009</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG 33 (52PCS)</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>USJ-PPO-2566</t>
+        </is>
+      </c>
+      <c r="Q505" t="n">
+        <v>220</v>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>CTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Doc304</t>
+        </is>
+      </c>
+      <c r="B506" s="9" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>OPENING BALANCE</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>KWI-GRN-NZ-0001</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI GREEN KIWI 10KG 36 (104PCS)</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>USJ-GL-9065</t>
+        </is>
+      </c>
+      <c r="Q506" t="n">
+        <v>19</v>
+      </c>
+      <c r="R506" t="inlineStr">
         <is>
           <t>CTN</t>
         </is>
@@ -27467,9 +31424,6 @@
       <c r="J2" t="n">
         <v>18</v>
       </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>SIZE: desc=135, item_code=138</t>
@@ -27479,9 +31433,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N2" t="n">
-        <v/>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -27547,9 +31498,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
@@ -27614,9 +31562,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
@@ -27663,12 +31608,6 @@
       <c r="I5" t="n">
         <v>24</v>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>SIZE: desc=24, item_code=58MM</t>
@@ -27678,9 +31617,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N5" t="n">
-        <v/>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -27731,9 +31667,6 @@
       <c r="J6" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=citrx</t>
@@ -27743,9 +31676,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N6" t="n">
-        <v/>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -27811,9 +31741,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -27863,9 +31790,6 @@
       <c r="J8" t="n">
         <v>18</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>SIZE: desc=120, item_code=110</t>
@@ -27875,9 +31799,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v/>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -27925,12 +31846,6 @@
       <c r="I9" t="n">
         <v>135</v>
       </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>SIZE: desc=135, item_code=216</t>
@@ -27940,9 +31855,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N9" t="n">
-        <v/>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -27990,12 +31902,6 @@
       <c r="I10" t="n">
         <v>150</v>
       </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>SIZE: desc=150, item_code=216</t>
@@ -28005,9 +31911,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N10" t="n">
-        <v/>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -28055,12 +31958,6 @@
       <c r="I11" t="n">
         <v>180</v>
       </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>SIZE: desc=180, item_code=216</t>
@@ -28070,9 +31967,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N11" t="n">
-        <v/>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28138,9 +32032,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -28190,9 +32081,6 @@
       <c r="J13" t="n">
         <v>18</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>SIZE: desc=120, item_code=110</t>
@@ -28202,9 +32090,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N13" t="n">
-        <v/>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -28255,9 +32140,6 @@
       <c r="J14" t="n">
         <v>18</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=mission</t>
@@ -28267,9 +32149,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N14" t="n">
-        <v/>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -28320,9 +32199,6 @@
       <c r="J15" t="n">
         <v>12</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>SIZE: desc=52, item_code=60</t>
@@ -28332,9 +32208,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N15" t="n">
-        <v/>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28385,9 +32258,6 @@
       <c r="J16" t="n">
         <v>18</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>SIZE: desc=80, item_code=216</t>
@@ -28397,9 +32267,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N16" t="n">
-        <v/>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -28450,9 +32317,6 @@
       <c r="J17" t="n">
         <v>18</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>SIZE: desc=90, item_code=216</t>
@@ -28462,9 +32326,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N17" t="n">
-        <v/>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -28515,9 +32376,6 @@
       <c r="J18" t="n">
         <v>18</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>SIZE: desc=100, item_code=216</t>
@@ -28527,9 +32385,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N18" t="n">
-        <v/>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -28580,9 +32435,6 @@
       <c r="J19" t="n">
         <v>18</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>SIZE: desc=150, item_code=216</t>
@@ -28592,9 +32444,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N19" t="n">
-        <v/>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -28645,9 +32494,6 @@
       <c r="J20" t="n">
         <v>18</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>SIZE: desc=150, item_code=216</t>
@@ -28657,9 +32503,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N20" t="n">
-        <v/>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -28710,9 +32553,6 @@
       <c r="J21" t="n">
         <v>18</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>SIZE: desc=180, item_code=216</t>
@@ -28722,9 +32562,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N21" t="n">
-        <v/>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -28775,9 +32612,6 @@
       <c r="J22" t="n">
         <v>18</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>SIZE: desc=180, item_code=216</t>
@@ -28787,9 +32621,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N22" t="n">
-        <v/>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -28840,9 +32671,6 @@
       <c r="J23" t="n">
         <v>12</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>SIZE: desc=52, item_code=48</t>
@@ -28852,9 +32680,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N23" t="n">
-        <v/>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -28920,9 +32745,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -28987,9 +32809,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -29054,9 +32873,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -29100,15 +32916,9 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v/>
-      </c>
       <c r="J27" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>WEIGHT: desc=3.0kg, item_code=4.2kg</t>
@@ -29118,9 +32928,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N27" t="n">
-        <v/>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -29186,9 +32993,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -29238,9 +33042,6 @@
       <c r="J29" t="n">
         <v>11</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>SIZE: desc=72, item_code=58MM</t>
@@ -29250,9 +33051,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N29" t="n">
-        <v/>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -29318,9 +33116,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
@@ -29385,9 +33180,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
@@ -29452,9 +33244,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -29501,9 +33290,6 @@
       <c r="I33" t="n">
         <v>110</v>
       </c>
-      <c r="J33" t="n">
-        <v/>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>AG</t>
@@ -29518,9 +33304,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N33" t="n">
-        <v/>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -29586,9 +33369,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
@@ -29653,9 +33433,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -29720,9 +33497,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -29787,9 +33561,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -29854,9 +33625,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
@@ -29921,9 +33689,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -29988,9 +33753,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -30055,9 +33817,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
@@ -30122,9 +33881,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
@@ -30174,9 +33930,6 @@
       <c r="J43" t="n">
         <v>18</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=bostock</t>
@@ -30186,9 +33939,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N43" t="n">
-        <v/>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -30239,9 +33989,6 @@
       <c r="J44" t="n">
         <v>18</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=bostock</t>
@@ -30251,9 +33998,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N44" t="n">
-        <v/>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -30304,9 +34048,6 @@
       <c r="J45" t="n">
         <v>18</v>
       </c>
-      <c r="K45" t="n">
-        <v/>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=bostock</t>
@@ -30316,9 +34057,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N45" t="n">
-        <v/>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -30384,9 +34122,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v/>
-      </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
@@ -30451,9 +34186,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
@@ -30518,9 +34250,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
@@ -30570,9 +34299,6 @@
       <c r="J49" t="n">
         <v>18</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=mission</t>
@@ -30582,9 +34308,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N49" t="n">
-        <v/>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -30635,9 +34358,6 @@
       <c r="J50" t="n">
         <v>20</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>SIZE: desc=175, item_code=198 | BRAND: desc=[domex superfresh], item_code=carati</t>
@@ -30647,9 +34367,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N50" t="n">
-        <v/>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -30700,9 +34417,6 @@
       <c r="J51" t="n">
         <v>11</v>
       </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>SIZE: desc=72, item_code=58MM</t>
@@ -30712,9 +34426,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N51" t="n">
-        <v/>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -30765,9 +34476,6 @@
       <c r="J52" t="n">
         <v>10</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=zespri</t>
@@ -30777,9 +34485,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N52" t="n">
-        <v/>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -30830,9 +34535,6 @@
       <c r="J53" t="n">
         <v>10</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=zespri</t>
@@ -30842,9 +34544,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N53" t="n">
-        <v/>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -30889,15 +34588,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v/>
-      </c>
-      <c r="J54" t="n">
-        <v/>
-      </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=naturipe farms</t>
@@ -30907,9 +34597,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N54" t="n">
-        <v/>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -30960,9 +34647,6 @@
       <c r="J55" t="n">
         <v>18</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>BRAND: desc=[sungarden], item_code=sunkist</t>
@@ -30972,9 +34656,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N55" t="n">
-        <v/>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -31019,15 +34700,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v/>
-      </c>
-      <c r="J56" t="n">
-        <v/>
-      </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=dof</t>
@@ -31037,9 +34709,6 @@
         <is>
           <t>CANNOT_PARSE</t>
         </is>
-      </c>
-      <c r="N56" t="n">
-        <v/>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -31105,9 +34774,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
@@ -31172,9 +34838,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
@@ -31239,9 +34902,6 @@
           <t>NO_EXACT_MATCH</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v/>
-      </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
@@ -31291,9 +34951,6 @@
       <c r="J60" t="n">
         <v>18</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=chislett farms</t>
@@ -31303,9 +34960,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N60" t="n">
-        <v/>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -31356,9 +35010,6 @@
       <c r="J61" t="n">
         <v>18</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=chislett farms</t>
@@ -31368,9 +35019,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N61" t="n">
-        <v/>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -31415,15 +35063,9 @@
           <t>bollo</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v/>
-      </c>
       <c r="J62" t="n">
         <v>10</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>WEIGHT: desc=10.0kg, item_code=6.5kg</t>
@@ -31433,9 +35075,6 @@
         <is>
           <t>CANNOT_PARSE</t>
         </is>
-      </c>
-      <c r="N62" t="n">
-        <v/>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -31483,12 +35122,6 @@
       <c r="I63" t="n">
         <v>500</v>
       </c>
-      <c r="J63" t="n">
-        <v/>
-      </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=agro valley</t>
@@ -31498,9 +35131,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N63" t="n">
-        <v/>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -31551,9 +35181,6 @@
       <c r="J64" t="n">
         <v>12</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=dutoit</t>
@@ -31563,9 +35190,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N64" t="n">
-        <v/>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -31610,15 +35234,9 @@
           <t>nifty</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v/>
-      </c>
       <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>BRAND: desc=[nifty], item_code=sunkist | WEIGHT: desc=1.0kg, item_code=15.0kg</t>
@@ -31628,9 +35246,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N65" t="n">
-        <v/>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -31678,12 +35293,6 @@
       <c r="I66" t="n">
         <v>700</v>
       </c>
-      <c r="J66" t="n">
-        <v/>
-      </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>BRAND: desc=[nifty], item_code=sunkist</t>
@@ -31693,9 +35302,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N66" t="n">
-        <v/>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -31746,9 +35352,6 @@
       <c r="J67" t="n">
         <v>18</v>
       </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>BRAND: desc=[sungarden], item_code=quenchas | WEIGHT: desc=18.0kg, item_code=13.0kg</t>
@@ -31758,9 +35361,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N67" t="n">
-        <v/>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -31811,9 +35411,6 @@
       <c r="J68" t="n">
         <v>18</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=sunkist</t>
@@ -31823,9 +35420,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N68" t="n">
-        <v/>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -31870,15 +35464,9 @@
           <t>bollo</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v/>
-      </c>
       <c r="J69" t="n">
         <v>10</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>WEIGHT: desc=10.0kg, item_code=6.5kg</t>
@@ -31888,9 +35476,6 @@
         <is>
           <t>CANNOT_PARSE</t>
         </is>
-      </c>
-      <c r="N69" t="n">
-        <v/>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -31938,12 +35523,6 @@
       <c r="I70" t="n">
         <v>88</v>
       </c>
-      <c r="J70" t="n">
-        <v/>
-      </c>
-      <c r="K70" t="n">
-        <v/>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>SIZE: desc=88, item_code=72 | BRAND: desc has NONE, item_code=letaba</t>
@@ -31953,9 +35532,6 @@
         <is>
           <t>CANNOT_PARSE</t>
         </is>
-      </c>
-      <c r="N70" t="n">
-        <v/>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -32000,15 +35576,9 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v/>
-      </c>
       <c r="J71" t="n">
         <v>8.6</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=golden ox</t>
@@ -32018,9 +35588,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N71" t="n">
-        <v/>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -32065,15 +35632,6 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v/>
-      </c>
-      <c r="J72" t="n">
-        <v/>
-      </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=naturipe farms</t>
@@ -32083,9 +35641,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N72" t="n">
-        <v/>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -32130,15 +35685,9 @@
           <t>seahawk</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v/>
-      </c>
       <c r="J73" t="n">
         <v>5</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>BRAND: desc=[seahawk], item_code=okanogan highlands</t>
@@ -32148,9 +35697,6 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N73" t="n">
-        <v/>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -32198,12 +35744,6 @@
       <c r="I74" t="n">
         <v>55</v>
       </c>
-      <c r="J74" t="n">
-        <v/>
-      </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>BRAND: desc has NONE, item_code=c5</t>
@@ -32213,12 +35753,2558 @@
         <is>
           <t>NO_EXACT_MATCH</t>
         </is>
-      </c>
-      <c r="N74" t="n">
-        <v/>
       </c>
       <c r="O74" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Stock_Row</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Best_Match_IC</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Best_Match_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SA ROYAL BEAUTY APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PPO0289</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SA KANGB RED FUJI APPLE 18KG 150</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B/KEE 3527</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SA KANGB RED FUJI APPLE 18KG 180</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B/KEE 3527</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>52</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SA NVF RED FUJI APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GL 7044</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>56</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Best desc match only 68%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>APL-PNKLDY-SA-0019</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>239</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GL 9511</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>242</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GL 9803</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>243</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 150</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GL 9803</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>244</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GL 9803</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>245</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GL 9803</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>246</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SA PINK LADY APPLE 18KG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GL 9803</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>355</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NZ PREMIER START PG APPLE 17.5KG 150</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GL 6647</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>360</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NZ PREMIER STAR PG APPLE 17.5KG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GL 3729</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>481</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG 18KG 135</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GL 7754</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>56</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>524</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GL 8660</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>526</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG 90</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GL 4696</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>91</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>527</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GL 4696</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>56</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>528</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NZ ENVY APPLE HG 18KG 120</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GL 4696</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>56</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>533</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NZ ENVY AG APPLE 18KG 120</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GL 2974</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>112</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>536</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE (2 LAYER) 8.5KG 70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GL 0367</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Best desc match only 45%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>APL-DZLE-NZ-0001</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NZ DAZZLE HG APPLES 17KG 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>537</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GL 0367</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Best desc match only 48%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>APL-DZLE-NZ-0001</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NZ DAZZLE HG APPLES 17KG 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>538</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG 110</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GL 0367</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Best desc match only 52%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>APL-DZLE-NZ-0001</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NZ DAZZLE HG APPLES 17KG 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>539</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NZ BOSTOCK LUMI APPLE 8.5KG 120</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GL 0367</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Best desc match only 52%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>APL-DZLE-NZ-0001</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NZ DAZZLE HG APPLES 17KG 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>595</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GL 7128</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>605</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SA INSEA GRANNY SMITH APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GL 6628</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Best desc match only 55%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PR-FRLE-SA-0055</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SA INSEA FORELLE PEAR 12KG 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>611</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SA KANGB GRANNY SMITH APPLE 18KG 165</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GL 6049</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>128</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>614</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SA C5 GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GL 6049</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>26</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>637</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH 18KG 120</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>UPT 9630</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>47</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>647</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH 18KG 150</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UPT5788</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>662</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 216</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B/KEE 3946</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>675</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 135</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GL 1143</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>56</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>687</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SA DUTOIT GRANNY SMITH APPLE 18KG 135</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GL 3522</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>26</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>691</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SA KROMCO GRANNY SMITH 18KG 90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MK26071062</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>86</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>692</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SA KROMCO GRANNY SMITH 18KG 110</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MK26071062</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>56</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>767</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SA SY LEMON 15KG 113</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GL 7270</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>160</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Best desc match only 29%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GRP-BLKSDLS-EGY-0002</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>787</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SA SY LEMON 15KG 100</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GL 7952</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>160</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>824</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SA NATBL NOVA MANDARIN 10KG 3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GL 8306</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>834</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG 2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GL 5257</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>104</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>835</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GL 5257</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>254</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>837</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SA SKIST ARC NADORCOTT MANDARIN 10KG 3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GL 5257</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>104</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>885</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SA VALENCIA 15KG 72</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FF0840</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>900</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 72</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GL 4717</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>901</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 88</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GL 4717</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>75</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>902</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 88</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GL 4717</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>144</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>903</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SA CITRIX MIDNIGHT VALENCIA 15KG 105</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GL 4717</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>80</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>911</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHINA NAVEL 14KG 64</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PPO8849</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SA SY NAVEL ORANGE 15KG 56</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GL 6780</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>107</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GL 4070</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>62</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 60</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GL 4070</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>30</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SA SKIST NEWHALL NAVEL ORANGE 15KG 65</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GL 4070</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SA CARA CARA ORANGES 15KG 55</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GL 3877</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>45</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 60</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 65</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>26</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 88</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>175</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SA SKIST CARA CARA ORANGES 15KG 105</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>219</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>INDIA POMEGRANATES 3KG 10</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GL 6990</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>109</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>INDIA POMEGRANATES 3KG 12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GL 6990</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>360</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CHINA HUANG GUAN 13KG 48</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FF 1378</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>56</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 170GM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PPO 0599</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>42</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 170GM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PPO 0599</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>90</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CHINA FRAGRANT PEAR 6.5KG 180GM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PPO 0599</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>72</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SA DUTOIT PACKHAMS TRIUMPH PEAR 12KG 60</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GL 4758</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>28</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SA C5 PACKHAM PEAR 12KG 60</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GL 7350</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>240</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CHINA RED GLOBE 6.5KG 11 X 800GM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FF 1320</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>35</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>USA SUPERSWEET IVORY GRAPE 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AIR 2912</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>USA BLUE STONE SUGAR CRUNCH GRAPES 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AIR 4752</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>USA AIR CHIEF MIDNIGHT BEAUTY GRAPES 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AIR 4752</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>25</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1327</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>USA KRISSY 8.6KG / BEBOP 19LB / 8.6KG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AIR 4752</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>45</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1351</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CHINA SHINE MUSCAT 8X500</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PPO 3906</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1356</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CHINA GB SHINE MUSCAT 10X500G 22MM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GL 5160</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>230</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1360</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G 22MM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GL 8283</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>215</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1361</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GL 8283</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>115</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GL 8283</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>230</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1363</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHINA LILIE SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>GL 8283</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>110</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1366</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CHINA GENERIC SHINE MUSCAT 10X500G</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GL 9804</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>920</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CHINA GB AUTUMN ROYAL GRAPE (BLACK SEED) 10X500GM 20-28MM</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GL 0443</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>115</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GL 2552</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>125</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GL 2552</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>75</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EGYPT BLACK GRAPES 500GM 10X500GM XL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GL 2552</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>125</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EGYPT AGRO VALLEY GRAPE 10X500GM</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GL 5426</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>404</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CHINA CRIMSON GRAPE 10X500G</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GL 1394</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Best desc match only 55%</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>GRP-SHNMSCT-CN-0001</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CHINA SHINE MUSCAT 10X500G 22MM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 18</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FF 1378</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>143</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 18</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>280</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG 24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>384</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VIETNAM DRAGON FRUIT 9KG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>280</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ZIMBABWE BLUEBERRY (JUMBO TUBE) 10X200G 18MM</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FF26071376</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>38</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>USA STRAWBERRIES - SWEET DARLING 12X125GM 13 X 250G</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AIR 5352</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>240</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>USA BORTON FRUIT SWEET CHERRY 9KG 9.5ROW</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AIR2360</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>USA GOLD PRIZE SWEET CHERRY 5KG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AIR 2962</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>195</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Best desc match only 69%</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CHRY-SWTHRT-USA-0001</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>USA SEAHAWK SWEET CHERRY 5KG 9ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KOREA WHITE PEACHES 2PCS 2S 2PCS X 6PKT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AIR 1944</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>96</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>USA MOUNTAIN VIEW EMERALD BEAUTY PLUMS 11.3KG 16X1LB</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AIR 1863</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>51</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 14</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>154</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 16</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>221</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 18</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>150</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CHINA YELLOW SKIN KEITT MANGO 14KG 20</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>137</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 16</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>36</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 18</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>85</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 20</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>106</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 24</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>478</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CHINA GREEN SKIN KEITT MANGO 14KG 28</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PPO 3748</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>150</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PPO 3748</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>110</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI SUNGOLD KIWI 5.6KG 33 (52PCS)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PPO2566</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>220</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1698</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NZ ZESPRI GREEN KIWI 10KG 36 (104PCS)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GL 9065</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>19</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No container match in final4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Total flagged: 104 items</t>
+        </is>
       </c>
     </row>
   </sheetData>
